--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486925_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486925_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7697</v>
+        <v>3.8144</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.6569</v>
+        <v>-0.8119</v>
       </c>
       <c r="F2" t="n">
-        <v>5.4266</v>
+        <v>4.6263</v>
       </c>
       <c r="G2" t="n">
         <v>1.1859</v>
@@ -610,13 +610,13 @@
         <v>3.6962</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9501</v>
+        <v>0.9948</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5189</v>
+        <v>0.3639</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4312</v>
+        <v>0.6309</v>
       </c>
       <c r="V2" t="n">
         <v>-0.008999999999999999</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1849</v>
+        <v>2.0788</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.2485</v>
+        <v>-1.0582</v>
       </c>
       <c r="F3" t="n">
-        <v>3.4335</v>
+        <v>3.1371</v>
       </c>
       <c r="G3" t="n">
         <v>-0.8272</v>
@@ -688,13 +688,13 @@
         <v>3.0801</v>
       </c>
       <c r="S3" t="n">
-        <v>2.0766</v>
+        <v>0.9705</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6773</v>
+        <v>0.8676</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3993</v>
+        <v>0.1029</v>
       </c>
       <c r="V3" t="n">
         <v>-0.1179</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7048</v>
+        <v>1.4055</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1373</v>
+        <v>0.5713</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5675</v>
+        <v>0.8343</v>
       </c>
       <c r="G4" t="n">
         <v>-0.2686</v>
@@ -766,13 +766,13 @@
         <v>3.6962</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3995</v>
+        <v>0.3012</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.09719999999999999</v>
+        <v>0.3368</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3024</v>
+        <v>-0.0356</v>
       </c>
       <c r="V4" t="n">
         <v>-1.2965</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. CARRASCO MARTIN</t>
+          <t>P. SALA VALLMAJO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1065</v>
+        <v>-0.0859</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1123</v>
+        <v>0.0936</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0058</v>
+        <v>-0.1795</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4304</v>
+        <v>-0.7154</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1752</v>
+        <v>-0.6392</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2552</v>
+        <v>-0.07630000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0195</v>
+        <v>0.0395</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0195</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.0395</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4498</v>
+        <v>-0.7549</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1947</v>
+        <v>-0.6392</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2552</v>
+        <v>-0.1157</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2053</v>
+        <v>0.616</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2053</v>
+        <v>0.616</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1186</v>
+        <v>0.0135</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1317</v>
+        <v>0.0542</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2503</v>
+        <v>-0.0407</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. SALA VALLMAJO</t>
+          <t>J. CARRASCO MARTIN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3156</v>
+        <v>-0.225</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-0.1123</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2388</v>
+        <v>-0.1128</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7154</v>
+        <v>-0.4304</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6392</v>
+        <v>-0.1752</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.07630000000000001</v>
+        <v>-0.2552</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0395</v>
+        <v>0.0195</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.0195</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0395</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7549</v>
+        <v>-0.4498</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6392</v>
+        <v>-0.1947</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1157</v>
+        <v>-0.2552</v>
       </c>
       <c r="P6" t="n">
-        <v>0.616</v>
+        <v>0.2053</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.616</v>
+        <v>0.2053</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2162</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1163</v>
+        <v>-0.1317</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0999</v>
+        <v>0.1317</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3231</v>
+        <v>-0.2558</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6046</v>
+        <v>-0.9227</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2816</v>
+        <v>0.6669</v>
       </c>
       <c r="G7" t="n">
         <v>0.674</v>
@@ -1000,13 +1000,13 @@
         <v>2.6694</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2077</v>
+        <v>-0.1405</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7441</v>
+        <v>-0.0622</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4636</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="V7" t="n">
         <v>-1.4053</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6123</v>
+        <v>-0.55</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8344</v>
+        <v>-1.0091</v>
       </c>
       <c r="F8" t="n">
-        <v>0.222</v>
+        <v>0.4592</v>
       </c>
       <c r="G8" t="n">
         <v>-2.5014</v>
@@ -1078,13 +1078,13 @@
         <v>3.0801</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3956</v>
+        <v>-0.3332</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.2361</v>
+        <v>-0.4109</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1595</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>0.2312</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1629</v>
+        <v>-1.1846</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.7006</v>
+        <v>-4.0187</v>
       </c>
       <c r="F9" t="n">
-        <v>2.5377</v>
+        <v>2.8342</v>
       </c>
       <c r="G9" t="n">
         <v>-4.5558</v>
@@ -1156,13 +1156,13 @@
         <v>3.0801</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.143</v>
+        <v>-0.1647</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.1281</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.333</v>
+        <v>-0.0366</v>
       </c>
       <c r="V9" t="n">
         <v>3.5359</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.8853</v>
+        <v>-3.6851</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7567</v>
+        <v>-2.5862</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1286</v>
+        <v>-1.0989</v>
       </c>
       <c r="G10" t="n">
         <v>-2.9596</v>
@@ -1234,13 +1234,13 @@
         <v>0.8214</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7203000000000001</v>
+        <v>-0.5202</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5115</v>
+        <v>-0.341</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2088</v>
+        <v>-0.1791</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.6567</v>
+        <v>-5.0685</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.429</v>
+        <v>-3.7816</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2276</v>
+        <v>-1.2869</v>
       </c>
       <c r="G11" t="n">
         <v>-2.5869</v>
@@ -1312,13 +1312,13 @@
         <v>0.616</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3943</v>
+        <v>-0.0175</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3834</v>
+        <v>0.0309</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0109</v>
+        <v>-0.0484</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.403</v>
+        <v>-3.756200000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-15.2825</v>
+        <v>-13.6358</v>
       </c>
       <c r="F12" t="n">
-        <v>9.879699999999998</v>
+        <v>9.879900000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-12.9854</v>
@@ -1369,7 +1369,7 @@
         <v>-8.4131</v>
       </c>
       <c r="L12" t="n">
-        <v>1.9581</v>
+        <v>1.958100000000001</v>
       </c>
       <c r="M12" t="n">
         <v>-6.5304</v>
@@ -1390,10 +1390,10 @@
         <v>21.5608</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5426999999999995</v>
+        <v>1.1039</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.067299999999999</v>
+        <v>0.5795000000000002</v>
       </c>
       <c r="U12" t="n">
         <v>0.5245</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.2245</v>
+        <v>7.4023</v>
       </c>
       <c r="E13" t="n">
-        <v>4.9646</v>
+        <v>4.5462</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2599</v>
+        <v>2.8562</v>
       </c>
       <c r="G13" t="n">
         <v>5.9517</v>
@@ -1468,13 +1468,13 @@
         <v>2.2588</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5951</v>
+        <v>0.773</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5693</v>
+        <v>0.1509</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0259</v>
+        <v>0.6221</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3491</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.7489</v>
+        <v>4.4035</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1909</v>
+        <v>0.9231</v>
       </c>
       <c r="F14" t="n">
-        <v>2.558</v>
+        <v>3.4804</v>
       </c>
       <c r="G14" t="n">
         <v>8.5465</v>
@@ -1546,13 +1546,13 @@
         <v>2.4641</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.5121</v>
+        <v>0.1424</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0966</v>
+        <v>-0.3644</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4155</v>
+        <v>0.5068</v>
       </c>
       <c r="V14" t="n">
         <v>-0.5893</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8368</v>
+        <v>2.1157</v>
       </c>
       <c r="E15" t="n">
         <v>0.3353</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5015</v>
+        <v>1.7804</v>
       </c>
       <c r="G15" t="n">
         <v>2.4101</v>
@@ -1624,13 +1624,13 @@
         <v>0.616</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0427</v>
+        <v>0.3216</v>
       </c>
       <c r="T15" t="n">
         <v>0.0155</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0272</v>
+        <v>0.3062</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3711</v>
+        <v>1.1636</v>
       </c>
       <c r="E16" t="n">
         <v>1.3949</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0238</v>
+        <v>-0.2313</v>
       </c>
       <c r="G16" t="n">
         <v>1.6845</v>
@@ -1702,13 +1702,13 @@
         <v>0.4107</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4545</v>
+        <v>0.247</v>
       </c>
       <c r="T16" t="n">
         <v>0.0736</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3809</v>
+        <v>0.1734</v>
       </c>
       <c r="V16" t="n">
         <v>-1.1786</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7573</v>
+        <v>0.9874000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.4361</v>
+        <v>-1.2269</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1934</v>
+        <v>2.2143</v>
       </c>
       <c r="G17" t="n">
         <v>0.8827</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1254</v>
+        <v>0.1047</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1976</v>
+        <v>0.0116</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0722</v>
+        <v>0.0931</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. NIANG BEYE</t>
+          <t>E. KALU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4013</v>
+        <v>0.0916</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.4048</v>
+        <v>-2.7394</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0035</v>
+        <v>2.831</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4645</v>
+        <v>-1.0247</v>
       </c>
       <c r="H18" t="n">
-        <v>1.4142</v>
+        <v>-1.0381</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.8786</v>
+        <v>0.0134</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3969</v>
+        <v>-1.794</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8794</v>
+        <v>-1.9913</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.2763</v>
+        <v>0.1973</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0675</v>
+        <v>0.7693</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5348000000000001</v>
+        <v>0.9532</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6022999999999999</v>
+        <v>-0.1839</v>
       </c>
       <c r="P18" t="n">
         <v>0.4107</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0267</v>
+        <v>-1.2321</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4374</v>
+        <v>1.6427</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8310999999999999</v>
+        <v>0.1163</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.283</v>
+        <v>0.0464</v>
       </c>
       <c r="U18" t="n">
-        <v>1.1141</v>
+        <v>0.0699</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.1786</v>
+        <v>0.5893</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6982</v>
+        <v>0.2402</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.4805</v>
+        <v>0.3491</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. KALU</t>
+          <t>S. NIANG BEYE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6058</v>
+        <v>-0.8111</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.1579</v>
+        <v>-2.5094</v>
       </c>
       <c r="F19" t="n">
-        <v>2.5521</v>
+        <v>1.6983</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.0247</v>
+        <v>-0.4645</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0381</v>
+        <v>1.4142</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0134</v>
+        <v>-1.8786</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.794</v>
+        <v>-0.3969</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.9913</v>
+        <v>0.8794</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1973</v>
+        <v>-1.2763</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7693</v>
+        <v>-0.0675</v>
       </c>
       <c r="N19" t="n">
-        <v>0.9532</v>
+        <v>0.5348000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1839</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="P19" t="n">
         <v>0.4107</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.2321</v>
+        <v>-1.0267</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6427</v>
+        <v>1.4374</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5810999999999999</v>
+        <v>0.4214</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3721</v>
+        <v>-0.3876</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.209</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5893</v>
+        <v>-1.1786</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2402</v>
+        <v>-0.6982</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3491</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0016</v>
+        <v>-0.9231</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2079</v>
+        <v>-1.4171</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2063</v>
+        <v>0.494</v>
       </c>
       <c r="G20" t="n">
         <v>2.7667</v>
@@ -2014,13 +2014,13 @@
         <v>0.8214</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3119</v>
+        <v>0.3904</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1858</v>
+        <v>-0.0234</v>
       </c>
       <c r="U20" t="n">
-        <v>0.126</v>
+        <v>0.4137</v>
       </c>
       <c r="V20" t="n">
         <v>-0.5893</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. HALL</t>
+          <t>G. MARTINEZ RIVERA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.095</v>
+        <v>-1.4765</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6245</v>
+        <v>-2.9566</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5295</v>
+        <v>1.4802</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.2114</v>
+        <v>-0.5405</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.1539</v>
+        <v>0.996</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.0576</v>
+        <v>-1.5365</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.1124</v>
+        <v>-1.2232</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.7967</v>
+        <v>0.0137</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3158</v>
+        <v>-1.2368</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.099</v>
+        <v>0.6827</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3572</v>
+        <v>0.9823</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7418</v>
+        <v>-0.2996</v>
       </c>
       <c r="P21" t="n">
-        <v>2.0534</v>
+        <v>-3.2855</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-5.3389</v>
       </c>
       <c r="R21" t="n">
         <v>2.0534</v>
       </c>
       <c r="S21" t="n">
-        <v>1.0631</v>
+        <v>-0.0077</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4879</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5750999999999999</v>
+        <v>-0.07729999999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>2.3573</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>3.5359</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. MARTINEZ RIVERA</t>
+          <t>S. HALL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.337</v>
+        <v>-1.6912</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5382</v>
+        <v>-3.0429</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2012</v>
+        <v>1.3517</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.5405</v>
+        <v>-4.2114</v>
       </c>
       <c r="H22" t="n">
-        <v>0.996</v>
+        <v>-2.1539</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.5365</v>
+        <v>-2.0576</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.2232</v>
+        <v>-3.1124</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0137</v>
+        <v>-1.7967</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2368</v>
+        <v>-1.3158</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6827</v>
+        <v>-1.099</v>
       </c>
       <c r="N22" t="n">
-        <v>0.9823</v>
+        <v>-0.3572</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2996</v>
+        <v>-0.7418</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.2855</v>
+        <v>2.0534</v>
       </c>
       <c r="Q22" t="n">
-        <v>-5.3389</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>2.0534</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1317</v>
+        <v>0.4668</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4879</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3562</v>
+        <v>0.3973</v>
       </c>
       <c r="V22" t="n">
-        <v>2.3573</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>3.5359</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0951</v>
+        <v>-3.7673</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3961</v>
+        <v>-3.1869</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.699</v>
+        <v>-0.5804</v>
       </c>
       <c r="G23" t="n">
         <v>-3.0157</v>
@@ -2248,13 +2248,13 @@
         <v>0.616</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6687</v>
+        <v>-0.3409</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3952</v>
+        <v>-0.186</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2735</v>
+        <v>-0.1549</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>5.402799999999999</v>
+        <v>7.494899999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-9.879799999999999</v>
+        <v>-9.8797</v>
       </c>
       <c r="F24" t="n">
-        <v>15.2826</v>
+        <v>17.3748</v>
       </c>
       <c r="G24" t="n">
         <v>12.9854</v>
@@ -2299,7 +2299,7 @@
         <v>2.6706</v>
       </c>
       <c r="J24" t="n">
-        <v>6.530299999999999</v>
+        <v>6.5303</v>
       </c>
       <c r="K24" t="n">
         <v>1.9015</v>
@@ -2317,7 +2317,7 @@
         <v>-1.9579</v>
       </c>
       <c r="P24" t="n">
-        <v>-7.187</v>
+        <v>-7.186999999999999</v>
       </c>
       <c r="Q24" t="n">
         <v>-21.5611</v>
@@ -2326,16 +2326,16 @@
         <v>14.3739</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5428000000000001</v>
+        <v>2.635</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5245</v>
+        <v>-0.5244</v>
       </c>
       <c r="U24" t="n">
-        <v>1.0672</v>
+        <v>3.1593</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.9383000000000004</v>
+        <v>-0.9382999999999999</v>
       </c>
       <c r="W24" t="n">
         <v>5.6754</v>
